--- a/data/trans_dic/POLIPATOLOGIA_Lim_2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_2-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,96; 19,1</t>
+          <t>10,76; 19,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 19,04</t>
+          <t>10,52; 19,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,43; 20,29</t>
+          <t>11,81; 19,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,16; 35,56</t>
+          <t>24,78; 36,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,68; 37,44</t>
+          <t>26,49; 37,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,88; 28,41</t>
+          <t>20,78; 28,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 26,29</t>
+          <t>18,65; 25,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,87; 27,21</t>
+          <t>19,57; 26,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,88; 22,76</t>
+          <t>17,33; 23,07</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,88; 22,67</t>
+          <t>15,15; 22,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 16,3</t>
+          <t>10,53; 16,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,27; 17,7</t>
+          <t>11,36; 18,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,15; 34,26</t>
+          <t>26,05; 34,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,88; 30,96</t>
+          <t>23,09; 30,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,2; 34,27</t>
+          <t>27,66; 34,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,35; 27,23</t>
+          <t>21,66; 27,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,45; 22,76</t>
+          <t>17,72; 22,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,07; 25,27</t>
+          <t>20,0; 25,05</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,52; 25,75</t>
+          <t>16,36; 25,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,85; 15,69</t>
+          <t>8,9; 15,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,26; 28,11</t>
+          <t>19,25; 27,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,84; 32,04</t>
+          <t>21,73; 31,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,33; 27,71</t>
+          <t>18,7; 27,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,02; 37,52</t>
+          <t>29,18; 36,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,63; 27,23</t>
+          <t>20,69; 27,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,91; 20,71</t>
+          <t>14,51; 20,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,61; 31,66</t>
+          <t>25,57; 31,58</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,14; 19,04</t>
+          <t>11,35; 19,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,16; 20,65</t>
+          <t>13,05; 20,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,55; 31,51</t>
+          <t>20,39; 31,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,05; 36,56</t>
+          <t>26,96; 36,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,19; 36,42</t>
+          <t>26,21; 36,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,75; 34,83</t>
+          <t>16,91; 35,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 26,61</t>
+          <t>20,42; 26,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,74; 27,6</t>
+          <t>21,08; 27,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,89; 31,2</t>
+          <t>18,12; 30,8</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,7; 28,14</t>
+          <t>16,58; 28,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,63; 20,53</t>
+          <t>10,64; 20,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,17; 18,33</t>
+          <t>9,99; 17,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,63; 54,53</t>
+          <t>40,84; 55,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,7; 35,48</t>
+          <t>23,37; 35,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 29,25</t>
+          <t>12,11; 29,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,3; 39,76</t>
+          <t>30,12; 39,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,73; 26,35</t>
+          <t>18,76; 26,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 22,58</t>
+          <t>13,26; 22,81</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,67; 28,69</t>
+          <t>18,4; 28,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,26; 23,96</t>
+          <t>14,09; 23,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,33; 30,03</t>
+          <t>21,15; 29,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,78; 38,67</t>
+          <t>28,51; 40,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,24; 32,56</t>
+          <t>22,05; 32,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,94; 42,28</t>
+          <t>32,79; 41,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,02; 32,68</t>
+          <t>24,93; 32,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,27; 27,0</t>
+          <t>19,56; 27,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,95; 34,52</t>
+          <t>28,03; 34,35</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,07; 18,88</t>
+          <t>12,78; 18,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,34; 17,26</t>
+          <t>11,38; 16,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,94; 26,64</t>
+          <t>18,96; 26,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,84; 30,79</t>
+          <t>23,78; 30,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,37; 25,0</t>
+          <t>18,21; 24,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,91; 44,93</t>
+          <t>15,68; 45,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,56; 24,08</t>
+          <t>19,35; 24,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,81; 20,29</t>
+          <t>15,89; 20,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,91; 34,18</t>
+          <t>18,58; 34,34</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,56; 16,75</t>
+          <t>11,45; 16,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,28; 18,77</t>
+          <t>13,37; 18,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,98; 13,33</t>
+          <t>4,26; 13,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,27; 26,39</t>
+          <t>20,26; 26,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,67; 27,16</t>
+          <t>21,08; 27,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,51; 29,06</t>
+          <t>23,64; 29,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,03; 21,01</t>
+          <t>16,66; 20,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,2; 22,27</t>
+          <t>18,01; 22,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,29; 20,09</t>
+          <t>10,41; 20,2</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,34</t>
+          <t>15,72; 18,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,72; 16,16</t>
+          <t>13,68; 16,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,6; 18,98</t>
+          <t>13,23; 19,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27,69; 30,8</t>
+          <t>27,84; 30,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,22; 27,3</t>
+          <t>24,29; 27,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,13; 32,18</t>
+          <t>23,51; 32,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,16; 24,31</t>
+          <t>22,25; 24,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,41; 21,46</t>
+          <t>19,38; 21,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,31; 25,31</t>
+          <t>20,14; 25,29</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32297; 56286</t>
+          <t>31707; 57156</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31265; 55926</t>
+          <t>30889; 57782</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35585; 63178</t>
+          <t>36797; 61685</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69410; 102145</t>
+          <t>71192; 103579</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77036; 108101</t>
+          <t>76466; 109352</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60464; 82284</t>
+          <t>60192; 82654</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>110331; 152997</t>
+          <t>108566; 150064</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>115733; 158505</t>
+          <t>113991; 156010</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>101446; 136831</t>
+          <t>104158; 138673</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75200; 114620</t>
+          <t>76573; 114825</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53086; 81917</t>
+          <t>52945; 84595</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58404; 91759</t>
+          <t>58885; 93574</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>136969; 179451</t>
+          <t>136461; 180171</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>119659; 161949</t>
+          <t>120784; 161433</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>140062; 176484</t>
+          <t>142427; 177653</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>219749; 280326</t>
+          <t>222987; 281173</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>179007; 233401</t>
+          <t>181722; 233748</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>207397; 261163</t>
+          <t>206624; 258822</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53529; 83438</t>
+          <t>53004; 82550</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28189; 49975</t>
+          <t>28348; 50102</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60871; 88857</t>
+          <t>60836; 87465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74486; 109274</t>
+          <t>74109; 108499</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61635; 93185</t>
+          <t>62889; 94087</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>101324; 130999</t>
+          <t>101860; 128478</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>137232; 181084</t>
+          <t>137608; 181706</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97668; 135596</t>
+          <t>95005; 134126</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>170342; 210626</t>
+          <t>170055; 210048</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41676; 71204</t>
+          <t>42465; 71383</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48685; 76387</t>
+          <t>48293; 76816</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64239; 98499</t>
+          <t>63722; 98051</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105195; 142193</t>
+          <t>104874; 142600</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>101434; 141064</t>
+          <t>101524; 141854</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79684; 165696</t>
+          <t>80425; 167832</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>155686; 203011</t>
+          <t>155805; 202831</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>157048; 209032</t>
+          <t>159627; 210729</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>156758; 245904</t>
+          <t>142872; 242785</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35517; 59841</t>
+          <t>35250; 60453</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22449; 43372</t>
+          <t>22470; 43868</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18170; 32769</t>
+          <t>17850; 31663</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89225; 119737</t>
+          <t>89684; 120803</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51795; 77559</t>
+          <t>51083; 77842</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29117; 75702</t>
+          <t>31350; 75815</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>130979; 171838</t>
+          <t>130164; 172002</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80500; 113243</t>
+          <t>80641; 114916</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53595; 98796</t>
+          <t>58017; 99806</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>51143; 78600</t>
+          <t>50422; 78436</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37511; 63039</t>
+          <t>37071; 62288</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57502; 80976</t>
+          <t>57024; 79998</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77782; 108296</t>
+          <t>79829; 112173</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58000; 88931</t>
+          <t>60230; 89281</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>84678; 108679</t>
+          <t>84296; 107811</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>138612; 181047</t>
+          <t>138131; 180246</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>103350; 144796</t>
+          <t>104903; 145251</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>147190; 181832</t>
+          <t>147611; 180938</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>86650; 125123</t>
+          <t>84679; 124668</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>74435; 113322</t>
+          <t>74709; 111214</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118243; 166317</t>
+          <t>118333; 163599</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>165425; 213605</t>
+          <t>164993; 212072</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>126984; 172799</t>
+          <t>125856; 170438</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>152100; 381542</t>
+          <t>133156; 382248</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>265327; 326614</t>
+          <t>262474; 326661</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>213134; 273504</t>
+          <t>214184; 272580</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>263846; 503668</t>
+          <t>273716; 506079</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>90101; 130469</t>
+          <t>89227; 128357</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>103385; 146120</t>
+          <t>104065; 144283</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>36918; 123773</t>
+          <t>39547; 124649</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>166971; 217408</t>
+          <t>166911; 216825</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>170739; 224375</t>
+          <t>174121; 225072</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>168716; 208603</t>
+          <t>169700; 209324</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>272970; 336781</t>
+          <t>267032; 334373</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>292000; 357444</t>
+          <t>288975; 356937</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>169348; 330763</t>
+          <t>171320; 332537</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>539147; 628616</t>
+          <t>538765; 628083</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>465684; 548403</t>
+          <t>464515; 548687</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>470623; 656562</t>
+          <t>457566; 659443</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>985463; 1095935</t>
+          <t>990630; 1099426</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>858554; 967781</t>
+          <t>860858; 968200</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>895754; 1194646</t>
+          <t>872848; 1194874</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1547932; 1698386</t>
+          <t>1554153; 1693328</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1346697; 1488780</t>
+          <t>1344647; 1484176</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1456828; 1814962</t>
+          <t>1444766; 1814112</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_Lim_2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_2-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 19,39</t>
+          <t>10,73; 19,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,52; 19,67</t>
+          <t>10,58; 19,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,81; 19,81</t>
+          <t>11,91; 19,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,78; 36,06</t>
+          <t>24,1; 35,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,49; 37,88</t>
+          <t>26,01; 37,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,78; 28,54</t>
+          <t>20,71; 27,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,65; 25,78</t>
+          <t>18,71; 25,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,57; 26,78</t>
+          <t>19,3; 26,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,33; 23,07</t>
+          <t>17,26; 22,48</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,15; 22,71</t>
+          <t>14,37; 22,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 16,83</t>
+          <t>10,46; 16,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,36; 18,05</t>
+          <t>11,31; 17,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,05; 34,4</t>
+          <t>25,64; 34,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 30,86</t>
+          <t>23,04; 30,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,66; 34,5</t>
+          <t>27,47; 34,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,66; 27,32</t>
+          <t>21,39; 27,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,72; 22,79</t>
+          <t>17,61; 22,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,0; 25,05</t>
+          <t>20,27; 25,36</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,36; 25,47</t>
+          <t>16,38; 25,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 15,73</t>
+          <t>8,69; 15,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,25; 27,67</t>
+          <t>19,01; 27,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,73; 31,82</t>
+          <t>21,45; 31,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,7; 27,98</t>
+          <t>18,61; 28,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,18; 36,8</t>
+          <t>29,06; 36,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,69; 27,32</t>
+          <t>20,41; 27,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 20,48</t>
+          <t>14,9; 20,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,57; 31,58</t>
+          <t>25,47; 31,21</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 19,09</t>
+          <t>11,57; 19,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,05; 20,76</t>
+          <t>12,82; 20,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,39; 31,37</t>
+          <t>19,06; 29,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,96; 36,66</t>
+          <t>27,44; 36,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,21; 36,63</t>
+          <t>26,25; 36,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 35,28</t>
+          <t>29,88; 38,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,42; 26,59</t>
+          <t>20,5; 26,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,08; 27,83</t>
+          <t>20,92; 27,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 30,8</t>
+          <t>25,9; 32,42</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,58; 28,43</t>
+          <t>16,26; 28,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,64; 20,77</t>
+          <t>10,89; 20,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,99; 17,71</t>
+          <t>9,34; 16,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,84; 55,01</t>
+          <t>40,35; 52,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,37; 35,61</t>
+          <t>23,53; 35,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,11; 29,3</t>
+          <t>22,91; 30,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,12; 39,8</t>
+          <t>29,89; 39,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,76; 26,74</t>
+          <t>18,65; 26,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,26; 22,81</t>
+          <t>17,62; 23,15</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,4; 28,63</t>
+          <t>18,8; 29,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,09; 23,67</t>
+          <t>14,05; 23,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,15; 29,67</t>
+          <t>20,58; 29,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,51; 40,06</t>
+          <t>28,25; 39,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,05; 32,69</t>
+          <t>21,67; 32,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,79; 41,94</t>
+          <t>32,49; 41,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,93; 32,53</t>
+          <t>24,46; 32,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,56; 27,09</t>
+          <t>19,21; 26,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,03; 34,35</t>
+          <t>27,96; 34,38</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,78; 18,81</t>
+          <t>12,82; 18,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,38; 16,94</t>
+          <t>11,29; 17,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,96; 26,21</t>
+          <t>19,24; 25,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,78; 30,56</t>
+          <t>24,03; 31,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,21; 24,65</t>
+          <t>17,91; 24,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,68; 45,01</t>
+          <t>40,2; 46,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,35; 24,08</t>
+          <t>19,52; 23,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,89; 20,22</t>
+          <t>15,89; 19,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,58; 34,34</t>
+          <t>30,88; 35,88</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,45; 16,48</t>
+          <t>11,38; 16,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,37; 18,53</t>
+          <t>13,22; 19,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,26; 13,42</t>
+          <t>10,22; 14,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,26; 26,32</t>
+          <t>20,46; 26,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,08; 27,24</t>
+          <t>21,0; 26,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,64; 29,16</t>
+          <t>22,78; 27,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,66; 20,86</t>
+          <t>17,04; 21,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,01; 22,24</t>
+          <t>18,01; 22,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,41; 20,2</t>
+          <t>17,23; 20,61</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,72; 18,33</t>
+          <t>15,65; 18,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,68; 16,16</t>
+          <t>13,71; 16,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,23; 19,06</t>
+          <t>16,91; 19,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27,84; 30,9</t>
+          <t>27,74; 30,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,32</t>
+          <t>24,22; 27,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,51; 32,19</t>
+          <t>31,23; 33,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,25; 24,24</t>
+          <t>22,12; 24,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,38; 21,39</t>
+          <t>19,49; 21,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,14; 25,29</t>
+          <t>24,43; 26,52</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47896</t>
+          <t>49749</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71186</t>
+          <t>77050</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119082</t>
+          <t>126799</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31707; 57156</t>
+          <t>31631; 56326</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30889; 57782</t>
+          <t>31074; 56075</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36797; 61685</t>
+          <t>37961; 62074</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71192; 103579</t>
+          <t>69227; 103028</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76466; 109352</t>
+          <t>75096; 108559</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60192; 82654</t>
+          <t>65457; 88233</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>108566; 150064</t>
+          <t>108886; 151265</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>113991; 156010</t>
+          <t>112433; 154804</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>104158; 138673</t>
+          <t>109555; 142704</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74001</t>
+          <t>76427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>158919</t>
+          <t>167745</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>232919</t>
+          <t>244172</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76573; 114825</t>
+          <t>72621; 111821</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52945; 84595</t>
+          <t>52582; 84329</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58885; 93574</t>
+          <t>60021; 95397</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>136461; 180171</t>
+          <t>134312; 179449</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>120784; 161433</t>
+          <t>120533; 162032</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>142427; 177653</t>
+          <t>150101; 186764</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>222987; 281173</t>
+          <t>220126; 282699</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>181722; 233748</t>
+          <t>180655; 235468</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>206624; 258822</t>
+          <t>218338; 273127</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73897</t>
+          <t>73318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>114958</t>
+          <t>117196</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>188855</t>
+          <t>190514</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53004; 82550</t>
+          <t>53066; 83441</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28348; 50102</t>
+          <t>27683; 48587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60836; 87465</t>
+          <t>60086; 87816</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74109; 108499</t>
+          <t>73147; 106545</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>62889; 94087</t>
+          <t>62601; 96725</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>101860; 128478</t>
+          <t>103559; 131548</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>137608; 181706</t>
+          <t>135718; 180967</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95005; 134126</t>
+          <t>97551; 136656</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>170055; 210048</t>
+          <t>171275; 209875</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79180</t>
+          <t>88890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>130191</t>
+          <t>142965</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>231855</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42465; 71383</t>
+          <t>43281; 71429</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48293; 76816</t>
+          <t>47417; 75919</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63722; 98051</t>
+          <t>71103; 111151</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104874; 142600</t>
+          <t>106733; 141316</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>101524; 141854</t>
+          <t>101657; 140203</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80425; 167832</t>
+          <t>126068; 161888</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>155805; 202831</t>
+          <t>156428; 203558</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>159627; 210729</t>
+          <t>158408; 208484</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>142872; 242785</t>
+          <t>205958; 257799</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>26223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58868</t>
+          <t>61110</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>83189</t>
+          <t>87332</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35250; 60453</t>
+          <t>34577; 60108</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22470; 43868</t>
+          <t>23002; 43130</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17850; 31663</t>
+          <t>19213; 33933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89684; 120803</t>
+          <t>88610; 116305</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51083; 77842</t>
+          <t>51439; 78324</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31350; 75815</t>
+          <t>52446; 69462</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>130164; 172002</t>
+          <t>129168; 170762</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80641; 114916</t>
+          <t>80158; 113283</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58017; 99806</t>
+          <t>76559; 100592</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68064</t>
+          <t>67367</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95470</t>
+          <t>97953</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>163534</t>
+          <t>165319</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>50422; 78436</t>
+          <t>51510; 79684</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37071; 62288</t>
+          <t>36982; 62928</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57024; 79998</t>
+          <t>55710; 80124</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>79829; 112173</t>
+          <t>79112; 109914</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>60230; 89281</t>
+          <t>59191; 89145</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>84296; 107811</t>
+          <t>85683; 110270</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>138131; 180246</t>
+          <t>135494; 178322</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>104903; 145251</t>
+          <t>102992; 144002</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>147611; 180938</t>
+          <t>149459; 183735</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141257</t>
+          <t>161379</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>282409</t>
+          <t>336234</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>423666</t>
+          <t>497612</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>84679; 124668</t>
+          <t>85002; 124969</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>74709; 111214</t>
+          <t>74153; 112789</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118333; 163599</t>
+          <t>138449; 185034</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>164993; 212072</t>
+          <t>166763; 215563</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>125856; 170438</t>
+          <t>123816; 169164</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>133156; 382248</t>
+          <t>310354; 362075</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>262474; 326661</t>
+          <t>264798; 325334</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>214184; 272580</t>
+          <t>214190; 268796</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>273716; 506079</t>
+          <t>460668; 535187</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86479</t>
+          <t>97640</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>187603</t>
+          <t>209162</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>274082</t>
+          <t>306802</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>89227; 128357</t>
+          <t>88676; 129482</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>104065; 144283</t>
+          <t>102940; 147995</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>39547; 124649</t>
+          <t>81538; 115209</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>166911; 216825</t>
+          <t>168589; 219985</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>174121; 225072</t>
+          <t>173463; 221260</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>169700; 209324</t>
+          <t>189396; 230625</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>267032; 334373</t>
+          <t>273161; 336610</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>288975; 356937</t>
+          <t>289041; 353797</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>171320; 332537</t>
+          <t>280691; 335765</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>595095</t>
+          <t>640992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1099603</t>
+          <t>1209415</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1694698</t>
+          <t>1850407</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>538765; 628083</t>
+          <t>536420; 633209</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>464515; 548687</t>
+          <t>465378; 550763</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>457566; 659443</t>
+          <t>597395; 691624</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>990630; 1099426</t>
+          <t>987012; 1089080</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>860858; 968200</t>
+          <t>858479; 975038</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>872848; 1194874</t>
+          <t>1167141; 1265328</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1554153; 1693328</t>
+          <t>1545276; 1696504</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1344647; 1484176</t>
+          <t>1352608; 1490115</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1444766; 1814112</t>
+          <t>1775947; 1927855</t>
         </is>
       </c>
     </row>
